--- a/output/laminas_comunales/comunal_p_monto_aps_a_2018_atacama.xlsx
+++ b/output/laminas_comunales/comunal_p_monto_aps_a_2018_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,106 +375,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Alto del Carmen</t>
+          <t>Tierra Amarilla</t>
         </is>
       </c>
       <c r="C2">
-        <v>83152.5546875</v>
+        <v>93247.578125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="C3">
-        <v>77036.71875</v>
+        <v>93154.921875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="C4">
-        <v>72531.8046875</v>
+        <v>92844.546875</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Caldera</t>
         </is>
       </c>
       <c r="C5">
-        <v>71085.640625</v>
+        <v>87497.8359375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diego de Almagro</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="C6">
-        <v>68755.578125</v>
+        <v>86466.6171875</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="C7">
-        <v>67902.25</v>
+        <v>86389.3515625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Alto del Carmen</t>
         </is>
       </c>
       <c r="C8">
-        <v>67807.4375</v>
+        <v>83152.5546875</v>
       </c>
     </row>
     <row r="9">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>67469.234375</v>
+        <v>82866.75</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,2707 @@
         </is>
       </c>
       <c r="C10">
+        <v>81994.4921875</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>81462.6171875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>81434.578125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>79790.1796875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>79732.8828125</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>79719.3203125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>79584.15625</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>79096.6484375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>77704.2109375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>77036.71875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>75776.890625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>74733.515625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>74652.2890625</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>74074.65625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>73437.953125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>73241.4765625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>72531.8046875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>71995.9375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>71579.2421875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>71223.7578125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>71085.640625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>70493.46875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>69947.6640625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>69142.9296875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>68755.578125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>68208.03125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>68070.15625</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>68023.0625</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>67902.25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>67807.4375</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>67780.984375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>67469.234375</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>67290.6484375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>67261.5390625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>66800.0078125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C45">
         <v>66785.9765625</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>66779.9296875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>65871.8046875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>64933.296875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>64908.76171875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>64111.65625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>63494.69140625</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>63122.05859375</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>62466.09375</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>61815.4921875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>60886.2265625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>59870.8984375</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>59110.19921875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>56752.58984375</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>54815.62890625</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>53835.9609375</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>53554.37109375</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>53299.2578125</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>52139.4140625</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>51543.05859375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>57.342658996582</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>57.3033714294434</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>54.4715461730957</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>53.1194305419922</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>52.9126205444336</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>52.9051971435547</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>52.8290634155273</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>51.5418510437012</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>50.8849563598633</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>49.773754119873</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>49.3403701782227</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>49.2822952270508</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>49.2000007629395</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>48.7272720336914</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>48.6000518798828</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>48.550724029541</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>47.8935699462891</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>47.6426811218262</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>47.4646224975586</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>47.0967750549316</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>47.0588226318359</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>46.844181060791</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>46.8160362243652</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>46.5909080505371</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>46.3465538024902</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>46.0910148620605</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>46.036979675293</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>45.5999984741211</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>45.3083114624023</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>44.9477348327637</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>44.8354148864746</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>44.6691398620605</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>44.5868949890137</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>44.1717796325684</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>43.9486122131348</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>43.9261436462402</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>43.8756866455078</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>43.3719444274902</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>43.1818199157715</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>42.8015556335449</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>42.1568641662598</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>41.7218551635742</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>41.5598297119141</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>41.4849739074707</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>41.4414405822754</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>41.1610870361328</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>41.1042938232422</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>41.0919532775879</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>41.0904273986816</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>41.0282974243164</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>40.7999992370605</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>40.1960792541504</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>39.7101440429688</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>39.5306854248047</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>38.8349533081055</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>38.3924560546875</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>37.8676452636719</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>36.7344055175781</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>36.4583320617676</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>36.1510772705078</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>36.0576934814453</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>35.8907661437988</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>35.8490562438965</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>34.8275871276855</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>34.8115310668945</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>34.7560958862305</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>33.0143547058105</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>31.8181819915771</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>31.7663822174072</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>31.5884475708008</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>31.3280372619629</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>30.6306304931641</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>30.5280532836914</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>29.2062683105469</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>28.5067882537842</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>27.2357730865479</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>27.1844654083252</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>27.0979022979736</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>26.4423084259033</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>26.1363639831543</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>25.5072460174561</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>25.1101322174072</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>24.8868770599365</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>24.7272720336914</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>23.8123722076416</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>23.693380355835</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>23.440860748291</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>23.3009700775146</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>22.9357795715332</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>22.682445526123</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>22.051887512207</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>21.7236461639404</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>21.6335544586182</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>21.2139072418213</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>21.1408920288086</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>20.9482765197754</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>20.6220417022705</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>20.547945022583</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>20.4861106872559</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>20.3166217803955</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>19.786096572876</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>18.9542484283447</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>18.4959354400635</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>18.1415920257568</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>18.0280055999756</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>17.8743953704834</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>17.7562770843506</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>17.7368659973145</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>17.2284641265869</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>16.9064750671387</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>16.6418437957764</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>16.3538875579834</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>15.8892126083374</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>14.6252288818359</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>14.3920593261719</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>13.1221723556519</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>12.7348642349243</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>12.1818180084229</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>11.5177412033081</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>11.2211217880249</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>10.959792137146</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>10.5534105300903</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>10.3723402023315</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>10.2941179275513</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>9.29118728637695</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>8.185153961181641</v>
       </c>
     </row>
   </sheetData>
